--- a/assets/constructions/examples/ctd_inserts_dh1.xlsx
+++ b/assets/constructions/examples/ctd_inserts_dh1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,58 +579,77 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TDMX31750PKM WP40PD</t>
+          <t>S1155100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Top Drill Modular X</t>
+          <t>S1155100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TDMX31750PKM</t>
+          <t>S1155100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WID_TopDrillX_P</t>
+          <t>YG1_SpadeDrill_Y</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>k8</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>5.778</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -639,17 +658,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MNSH</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiN</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>WP40PD</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -660,7 +679,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -682,71 +701,84 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2019 / WIDIA Достижения</t>
+          <t>YG1/25 RUS_Сверление 2025</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrillX_P</t>
+          <t>YG1_SpadeDrill_Y</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>3299.5</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TDM0810UPM WU25PD</t>
+          <t>S1115156</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOP DRILL M1</t>
+          <t>S1115156</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TDM0810UPM</t>
+          <t>S1115156</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W10</t>
+          <t>YG1_SpadeDrill_3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>k8</t>
-        </is>
-      </c>
+        <v>47.63</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>1.474</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -755,7 +787,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MNSH</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -765,7 +797,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>WU25PD</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -776,7 +808,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -798,24 +830,43 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Master Catalog RU</t>
+          <t>YG1/25 RUS_Сверление 2025</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W10</t>
+          <t>YG1_SpadeDrill_3</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>77.93000000000001</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>7164.39</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TDM1240UPM WU25PD</t>
+          <t>TDMX26400PKM WP40PD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -825,17 +876,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOP DRILL M1</t>
+          <t>Top Drill Modular X</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TDM1240UPM</t>
+          <t>TDMX26400PKM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -845,11 +896,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W18</t>
+          <t>WID_TopDrillX_K</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12.4</v>
+        <v>26.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -859,7 +910,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.257</v>
+        <v>4.804</v>
       </c>
       <c r="M4" t="n">
         <v>140</v>
@@ -881,7 +932,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>WU25PD</t>
+          <t>WP40PD</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -914,24 +965,35 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Master Catalog RU</t>
+          <t>2019 / WIDIA Достижения</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W18</t>
+          <t>WIDIA_TopDrillX_K</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TDM2381UPM WU25PD</t>
+          <t>TDMX20239PKM WP40PD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -941,17 +1003,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOP DRILL M1</t>
+          <t>Top Drill Modular X</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TDM2381UPM</t>
+          <t>TDMX20239PKM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -961,11 +1023,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W32</t>
+          <t>WID_TopDrillX_E</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23.812</v>
+        <v>20.239</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -975,7 +1037,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.333</v>
+        <v>3.683</v>
       </c>
       <c r="M5" t="n">
         <v>140</v>
@@ -997,7 +1059,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>WU25PD</t>
+          <t>WP40PD</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1030,71 +1092,76 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Master Catalog RU</t>
+          <t>2019 / WIDIA Достижения</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W32</t>
+          <t>WIDIA_TopDrillX_E</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TDMX30163PKM WP40PD</t>
+          <t>S1160540</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Top Drill Modular X</t>
+          <t>S1160540</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TDMX30163PKM</t>
+          <t>S1160540</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WID_TopDrillX_O</t>
+          <t>YG1_SpadeDrill_4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>30.163</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>k8</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>5.489</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1103,17 +1170,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MNSH</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>WP40PD</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1124,7 +1191,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,17 +1213,36 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2019 / WIDIA Достижения</t>
+          <t>YG1/25 RUS_Сверление 2025</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrillX_O</t>
+          <t>YG1_SpadeDrill_4</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>9051.790000000001</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
